--- a/example/reference_results/3_primer_trimming/primer_trimming_summary.xlsx
+++ b/example/reference_results/3_primer_trimming/primer_trimming_summary.xlsx
@@ -362,7 +362,7 @@
     <t xml:space="preserve">Subject-R11-Timepoint-1</t>
   </si>
   <si>
-    <t xml:space="preserve">Subject-R11-Timepoint-1_filtered_Q20.fastq</t>
+    <t xml:space="preserve">Subject-R11-Timepoint-1_filtered_Q20.fastq.gz</t>
   </si>
   <si>
     <t xml:space="preserve">AGRGTTYGATYMTGGCTCAG</t>
@@ -377,19 +377,19 @@
     <t xml:space="preserve">Subject-R3-Timepoint-1</t>
   </si>
   <si>
-    <t xml:space="preserve">Subject-R3-Timepoint-1_filtered_Q20.fastq</t>
+    <t xml:space="preserve">Subject-R3-Timepoint-1_filtered_Q20.fastq.gz</t>
   </si>
   <si>
     <t xml:space="preserve">Subject-R3-Timepoint-2</t>
   </si>
   <si>
-    <t xml:space="preserve">Subject-R3-Timepoint-2_filtered_Q20.fastq</t>
+    <t xml:space="preserve">Subject-R3-Timepoint-2_filtered_Q20.fastq.gz</t>
   </si>
   <si>
     <t xml:space="preserve">Subject-R3-Timepoint-3</t>
   </si>
   <si>
-    <t xml:space="preserve">Subject-R3-Timepoint-3_filtered_Q20.fastq</t>
+    <t xml:space="preserve">Subject-R3-Timepoint-3_filtered_Q20.fastq.gz</t>
   </si>
   <si>
     <t xml:space="preserve">Primer</t>
@@ -944,7 +944,7 @@
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="23.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="42.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="45.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="13.71" hidden="0" customWidth="1"/>
@@ -1005,7 +1005,7 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>14.431</v>
+        <v>1.494</v>
       </c>
       <c r="E2" t="n">
         <v>5000</v>
@@ -1043,7 +1043,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>14.38</v>
+        <v>1.404</v>
       </c>
       <c r="E3" t="n">
         <v>5000</v>
@@ -1081,7 +1081,7 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>14.565</v>
+        <v>1.629</v>
       </c>
       <c r="E4" t="n">
         <v>5000</v>
@@ -1119,7 +1119,7 @@
         <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>14.518</v>
+        <v>1.515</v>
       </c>
       <c r="E5" t="n">
         <v>5000</v>
